--- a/AAAGameData/DataTables/Level/DefendAttackGroupTable.xlsx
+++ b/AAAGameData/DataTables/Level/DefendAttackGroupTable.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>#</t>
   </si>
@@ -44,7 +44,10 @@
     <t>AfterGroupIdentifier</t>
   </si>
   <si>
-    <t>UniqueValues</t>
+    <t>StartDelaySeconds</t>
+  </si>
+  <si>
+    <t>ExpectedEngagementSeconds</t>
   </si>
   <si>
     <t>int</t>
@@ -56,7 +59,7 @@
     <t>StringIntPair[]</t>
   </si>
   <si>
-    <t>Fix64[]</t>
+    <t>Fix64</t>
   </si>
   <si>
     <t>行号</t>
@@ -83,7 +86,169 @@
     <t>前置出兵组；空表示从防御阶段开始计时</t>
   </si>
   <si>
-    <t>[0]前置结束后的额外延迟秒（无前置时为阶段开始延迟）；[1]组内单位出兵间隔秒；[2]预计本组总持续时间秒（含行军与交战）；[3]行军速度覆盖，0表示使用全局防御最低速度</t>
+    <t>前置组固定出兵窗口结束后的延迟秒；无前置时为防御阶段开始延迟</t>
+  </si>
+  <si>
+    <t>从本组计时基准到预计接战时刻的秒数；固定出兵后，关卡内按当前首个玩家中转据点的导航距离反推移速</t>
+  </si>
+  <si>
+    <t>Lv_1_D2_East</t>
+  </si>
+  <si>
+    <t>Lv_1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Lv_1_Route_East</t>
+  </si>
+  <si>
+    <t>[Unit_HiredBodyguard,2]</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Lv_1_D2_North</t>
+  </si>
+  <si>
+    <t>Lv_1_Route_North</t>
+  </si>
+  <si>
+    <t>[Unit_HiredBodyguard,1]</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Lv_1_D2_West</t>
+  </si>
+  <si>
+    <t>Lv_1_Route_West</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Lv_1_D3_East</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Lv_1_D3_North</t>
+  </si>
+  <si>
+    <t>Lv_1_D3_West</t>
+  </si>
+  <si>
+    <t>Lv_1_D4_East</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>[Unit_HiredBodyguard,3]</t>
+  </si>
+  <si>
+    <t>Lv_1_D4_North</t>
+  </si>
+  <si>
+    <t>Lv_1_D4_West</t>
+  </si>
+  <si>
+    <t>Lv_2_D1_West</t>
+  </si>
+  <si>
+    <t>Lv_2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Lv_2_Route_West</t>
+  </si>
+  <si>
+    <t>[Unit_BoneButcher,1]</t>
+  </si>
+  <si>
+    <t>Lv_2_D1_SouthWest</t>
+  </si>
+  <si>
+    <t>Lv_2_Route_SouthWest</t>
+  </si>
+  <si>
+    <t>[Unit_CanMaker_Lv3,1]</t>
+  </si>
+  <si>
+    <t>Lv_2_D1_SouthEast</t>
+  </si>
+  <si>
+    <t>Lv_2_Route_SouthEast</t>
+  </si>
+  <si>
+    <t>Lv_3_D1_North</t>
+  </si>
+  <si>
+    <t>Lv_3</t>
+  </si>
+  <si>
+    <t>Lv_3_Route_North</t>
+  </si>
+  <si>
+    <t>[Unit_BoneButcher_Lv2,1],[Unit_Intern,1]</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Lv_3_D1_East</t>
+  </si>
+  <si>
+    <t>Lv_3_Route_East</t>
+  </si>
+  <si>
+    <t>[Unit_Intern,2]</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Lv_3_D1_SouthEast</t>
+  </si>
+  <si>
+    <t>Lv_3_Route_SouthEast</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>LvTest_D1_SouthWest</t>
+  </si>
+  <si>
+    <t>LvTest</t>
+  </si>
+  <si>
+    <t>LvTest_Route_SouthWest</t>
+  </si>
+  <si>
+    <t>LvTest_D1_SouthEast</t>
+  </si>
+  <si>
+    <t>LvTest_Route_SouthEast</t>
+  </si>
+  <si>
+    <t>[Unit_Poacher_Lv3,1]</t>
+  </si>
+  <si>
+    <t>LvTest_D1_West</t>
+  </si>
+  <si>
+    <t>LvTest_Route_West</t>
   </si>
 </sst>
 </file>
@@ -129,7 +294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -183,37 +348,43 @@
       <c r="J2" s="0" t="s">
         <v>10</v>
       </c>
+      <c r="K2" s="0" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>11</v>
-      </c>
       <c r="G3" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="0" t="s">
-        <v>12</v>
-      </c>
       <c r="J3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -221,31 +392,556 @@
         <v>0</v>
       </c>
       <c r="B4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="0">
+        <v>1</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0">
+        <v>2</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="0">
+        <v>3</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0">
+        <v>4</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0">
+        <v>5</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="0">
+        <v>6</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0">
+        <v>7</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0">
+        <v>8</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0">
+        <v>9</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="0">
+        <v>10</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0">
+        <v>11</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0">
+        <v>12</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0">
+        <v>13</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="0" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0">
+        <v>14</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0">
         <v>15</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="D19" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="0" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0">
         <v>16</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D20" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" s="0" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0">
         <v>17</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="D21" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0">
         <v>18</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="0" t="s">
-        <v>23</v>
+      <c r="D22" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="0" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Level/DefendAttackGroupTable.xlsx
+++ b/AAAGameData/DataTables/Level/DefendAttackGroupTable.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
@@ -92,27 +92,57 @@
     <t>从本组计时基准到预计接战时刻的秒数；固定出兵后，关卡内按当前首个玩家中转据点的导航距离反推移速</t>
   </si>
   <si>
+    <t>LvTest_D1_SouthEast</t>
+  </si>
+  <si>
+    <t>LvTest</t>
+  </si>
+  <si>
+    <t>LvTest_Route_SouthEast</t>
+  </si>
+  <si>
+    <t>[Unit_Poacher_Lv3,1]</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>LvTest_D1_SouthWest</t>
+  </si>
+  <si>
+    <t>LvTest_Route_SouthWest</t>
+  </si>
+  <si>
+    <t>[Unit_BoneButcher,1]</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>LvTest_D1_West</t>
+  </si>
+  <si>
+    <t>LvTest_Route_West</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>Lv_1_D2_East</t>
   </si>
   <si>
     <t>Lv_1</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Lv_1_Route_East</t>
   </si>
   <si>
     <t>[Unit_HiredBodyguard,2]</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>Lv_1_D2_North</t>
   </si>
   <si>
@@ -122,24 +152,15 @@
     <t>[Unit_HiredBodyguard,1]</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>Lv_1_D2_West</t>
   </si>
   <si>
     <t>Lv_1_Route_West</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>Lv_1_D3_East</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Lv_1_D3_North</t>
   </si>
   <si>
@@ -149,9 +170,6 @@
     <t>Lv_1_D4_East</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>[Unit_HiredBodyguard,3]</t>
   </si>
   <si>
@@ -161,42 +179,48 @@
     <t>Lv_1_D4_West</t>
   </si>
   <si>
+    <t>Lv_2_D1_SouthEast</t>
+  </si>
+  <si>
+    <t>Lv_2</t>
+  </si>
+  <si>
+    <t>TP2</t>
+  </si>
+  <si>
+    <t>[Unit_CanMaker_Lv3,1]</t>
+  </si>
+  <si>
+    <t>Lv_2_D1_SouthWest</t>
+  </si>
+  <si>
+    <t>TP3</t>
+  </si>
+  <si>
     <t>Lv_2_D1_West</t>
   </si>
   <si>
-    <t>Lv_2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Lv_2_Route_West</t>
-  </si>
-  <si>
-    <t>[Unit_BoneButcher,1]</t>
-  </si>
-  <si>
-    <t>Lv_2_D1_SouthWest</t>
-  </si>
-  <si>
-    <t>Lv_2_Route_SouthWest</t>
-  </si>
-  <si>
-    <t>[Unit_CanMaker_Lv3,1]</t>
-  </si>
-  <si>
-    <t>Lv_2_D1_SouthEast</t>
-  </si>
-  <si>
-    <t>Lv_2_Route_SouthEast</t>
+    <t>TP0</t>
+  </si>
+  <si>
+    <t>Lv_3_D1_East</t>
+  </si>
+  <si>
+    <t>Lv_3</t>
+  </si>
+  <si>
+    <t>Lv_3_Route_East</t>
+  </si>
+  <si>
+    <t>[Unit_Intern,2]</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>Lv_3_D1_North</t>
   </si>
   <si>
-    <t>Lv_3</t>
-  </si>
-  <si>
     <t>Lv_3_Route_North</t>
   </si>
   <si>
@@ -206,18 +230,6 @@
     <t>14</t>
   </si>
   <si>
-    <t>Lv_3_D1_East</t>
-  </si>
-  <si>
-    <t>Lv_3_Route_East</t>
-  </si>
-  <si>
-    <t>[Unit_Intern,2]</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>Lv_3_D1_SouthEast</t>
   </si>
   <si>
@@ -225,30 +237,6 @@
   </si>
   <si>
     <t>20</t>
-  </si>
-  <si>
-    <t>LvTest_D1_SouthWest</t>
-  </si>
-  <si>
-    <t>LvTest</t>
-  </si>
-  <si>
-    <t>LvTest_Route_SouthWest</t>
-  </si>
-  <si>
-    <t>LvTest_D1_SouthEast</t>
-  </si>
-  <si>
-    <t>LvTest_Route_SouthEast</t>
-  </si>
-  <si>
-    <t>[Unit_Poacher_Lv3,1]</t>
-  </si>
-  <si>
-    <t>LvTest_D1_West</t>
-  </si>
-  <si>
-    <t>LvTest_Route_West</t>
   </si>
 </sst>
 </file>
@@ -432,23 +420,23 @@
       <c r="E5" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="0">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="H5" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="0" t="s">
-        <v>30</v>
-      </c>
       <c r="I5" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J5" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="0" t="s">
         <v>31</v>
-      </c>
-      <c r="K5" s="0" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -456,28 +444,28 @@
         <v>2</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="0" t="s">
-        <v>28</v>
+      <c r="F6" s="0">
+        <v>1</v>
       </c>
       <c r="G6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="I6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="0" t="s">
         <v>35</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="0" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -485,28 +473,28 @@
         <v>3</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>28</v>
+      <c r="F7" s="0">
+        <v>1</v>
       </c>
       <c r="G7" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="0" t="s">
         <v>38</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="0" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -514,28 +502,28 @@
         <v>4</v>
       </c>
       <c r="D8" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="0">
+        <v>2</v>
+      </c>
+      <c r="G8" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="0" t="s">
-        <v>29</v>
-      </c>
       <c r="H8" s="0" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I8" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -543,28 +531,28 @@
         <v>5</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="F9" s="0">
+        <v>2</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J9" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="0" t="s">
         <v>31</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -572,28 +560,28 @@
         <v>6</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="F10" s="0">
+        <v>2</v>
       </c>
       <c r="G10" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="0" t="s">
         <v>38</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -601,28 +589,28 @@
         <v>7</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="F11" s="0">
+        <v>3</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I11" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -630,28 +618,28 @@
         <v>8</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="F12" s="0">
+        <v>3</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I12" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J12" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="0" t="s">
         <v>31</v>
-      </c>
-      <c r="K12" s="0" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -659,28 +647,28 @@
         <v>9</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="F13" s="0">
+        <v>3</v>
       </c>
       <c r="G13" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="0" t="s">
         <v>38</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="0" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -688,28 +676,28 @@
         <v>10</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>51</v>
+        <v>40</v>
+      </c>
+      <c r="F14" s="0">
+        <v>4</v>
       </c>
       <c r="G14" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="0" t="s">
-        <v>53</v>
-      </c>
       <c r="I14" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -717,28 +705,28 @@
         <v>11</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>51</v>
+        <v>40</v>
+      </c>
+      <c r="F15" s="0">
+        <v>4</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I15" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J15" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="0" t="s">
         <v>31</v>
-      </c>
-      <c r="K15" s="0" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -746,28 +734,28 @@
         <v>12</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>51</v>
+        <v>40</v>
+      </c>
+      <c r="F16" s="0">
+        <v>4</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="I16" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -775,28 +763,28 @@
         <v>13</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" s="0" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="F17" s="0">
+        <v>1</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I17" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -804,28 +792,28 @@
         <v>14</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E18" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="0">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="0" t="s">
-        <v>65</v>
-      </c>
       <c r="H18" s="0" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I18" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J18" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="0" t="s">
         <v>31</v>
-      </c>
-      <c r="K18" s="0" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="19">
@@ -833,28 +821,28 @@
         <v>15</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" s="0" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="F19" s="0">
+        <v>1</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="I19" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -862,28 +850,28 @@
         <v>16</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>51</v>
+        <v>64</v>
+      </c>
+      <c r="F20" s="0">
+        <v>1</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I20" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
@@ -891,28 +879,28 @@
         <v>17</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="0" t="s">
-        <v>51</v>
+        <v>64</v>
+      </c>
+      <c r="F21" s="0">
+        <v>1</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I21" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22">
@@ -920,28 +908,28 @@
         <v>18</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="0" t="s">
-        <v>51</v>
+        <v>64</v>
+      </c>
+      <c r="F22" s="0">
+        <v>1</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I22" s="0" t="s">
         <v>3</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Level/DefendAttackGroupTable.xlsx
+++ b/AAAGameData/DataTables/Level/DefendAttackGroupTable.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>#</t>
   </si>
@@ -32,13 +32,19 @@
     <t>LevelIdentifier</t>
   </si>
   <si>
-    <t>DefendRound</t>
+    <t>ActiveDays</t>
   </si>
   <si>
     <t>RouteIdentifier</t>
   </si>
   <si>
-    <t>Enemies</t>
+    <t>UnitIdentifier</t>
+  </si>
+  <si>
+    <t>InitialStrengthValue</t>
+  </si>
+  <si>
+    <t>CountGrowthWeight</t>
   </si>
   <si>
     <t>AfterGroupIdentifier</t>
@@ -50,13 +56,16 @@
     <t>ExpectedEngagementSeconds</t>
   </si>
   <si>
+    <t>Suffix</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>StringIntPair[]</t>
+    <t>int[]</t>
   </si>
   <si>
     <t>Fix64</t>
@@ -68,40 +77,55 @@
     <t>备注</t>
   </si>
   <si>
-    <t>代码内标识符</t>
+    <t>代码内标识符，由路线名和后缀派生；编辑器中只编辑后缀</t>
   </si>
   <si>
     <t>所属关卡标识</t>
   </si>
   <si>
-    <t>防御日，从1开始；超过最大日时重复最后一日并按无尽倍率成长</t>
+    <t>启用防御日；编辑器顶部选择天数后勾选，不生成按日实例</t>
   </si>
   <si>
     <t>路线标识符</t>
   </si>
   <si>
-    <t>固定兵种与数量；来源据点被占领后整组不出兵且不向其他据点转移</t>
-  </si>
-  <si>
-    <t>前置出兵组；空表示从防御阶段开始计时</t>
-  </si>
-  <si>
-    <t>前置组固定出兵窗口结束后的延迟秒；无前置时为防御阶段开始延迟</t>
-  </si>
-  <si>
-    <t>从本组计时基准到预计接战时刻的秒数；固定出兵后，关卡内按当前首个玩家中转据点的导航距离反推移速</t>
-  </si>
-  <si>
-    <t>LvTest_D1_SouthEast</t>
+    <t>单一兵种标识，不包含等级</t>
+  </si>
+  <si>
+    <t>初始橙髓等价战力；由兵种、数量和等级的非线性价值换算</t>
+  </si>
+  <si>
+    <t>新增强度在数量成长中的分配权重，0=全投等级，1=全投数量</t>
+  </si>
+  <si>
+    <t>前置小队；前置与本小队必须在同一天启用</t>
+  </si>
+  <si>
+    <t>前置小队固定出兵窗口结束后的延迟秒；无前置时为防御阶段开始延迟</t>
+  </si>
+  <si>
+    <t>从本小队计时基准到预计接战时刻的秒数</t>
+  </si>
+  <si>
+    <t>命名后缀，可空；同关卡同路线多小队时必须唯一</t>
+  </si>
+  <si>
+    <t>LvTest_Route_SouthEast</t>
   </si>
   <si>
     <t>LvTest</t>
   </si>
   <si>
-    <t>LvTest_Route_SouthEast</t>
-  </si>
-  <si>
-    <t>[Unit_Poacher_Lv3,1]</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Unit_Poacher</t>
+  </si>
+  <si>
+    <t>31.5</t>
+  </si>
+  <si>
+    <t>0.2</t>
   </si>
   <si>
     <t>0</t>
@@ -110,127 +134,115 @@
     <t>15</t>
   </si>
   <si>
-    <t>LvTest_D1_SouthWest</t>
-  </si>
-  <si>
     <t>LvTest_Route_SouthWest</t>
   </si>
   <si>
-    <t>[Unit_BoneButcher,1]</t>
+    <t>Unit_BoneButcher</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>0.25</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>LvTest_D1_West</t>
-  </si>
-  <si>
     <t>LvTest_Route_West</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>Lv_1_D2_East</t>
+    <t>Lv_1_Route_East</t>
   </si>
   <si>
     <t>Lv_1</t>
   </si>
   <si>
-    <t>Lv_1_Route_East</t>
-  </si>
-  <si>
-    <t>[Unit_HiredBodyguard,2]</t>
-  </si>
-  <si>
-    <t>Lv_1_D2_North</t>
+    <t>2,3,4</t>
+  </si>
+  <si>
+    <t>Unit_HiredBodyguard</t>
+  </si>
+  <si>
+    <t>5.1875</t>
+  </si>
+  <si>
+    <t>0.8</t>
   </si>
   <si>
     <t>Lv_1_Route_North</t>
   </si>
   <si>
-    <t>[Unit_HiredBodyguard,1]</t>
-  </si>
-  <si>
-    <t>Lv_1_D2_West</t>
+    <t>2.5</t>
   </si>
   <si>
     <t>Lv_1_Route_West</t>
   </si>
   <si>
-    <t>Lv_1_D3_East</t>
-  </si>
-  <si>
-    <t>Lv_1_D3_North</t>
-  </si>
-  <si>
-    <t>Lv_1_D3_West</t>
-  </si>
-  <si>
-    <t>Lv_1_D4_East</t>
-  </si>
-  <si>
-    <t>[Unit_HiredBodyguard,3]</t>
-  </si>
-  <si>
-    <t>Lv_1_D4_North</t>
-  </si>
-  <si>
-    <t>Lv_1_D4_West</t>
-  </si>
-  <si>
-    <t>Lv_2_D1_SouthEast</t>
+    <t>TP2</t>
   </si>
   <si>
     <t>Lv_2</t>
   </si>
   <si>
-    <t>TP2</t>
-  </si>
-  <si>
-    <t>[Unit_CanMaker_Lv3,1]</t>
-  </si>
-  <si>
-    <t>Lv_2_D1_SouthWest</t>
+    <t>Unit_CanMaker</t>
+  </si>
+  <si>
+    <t>5.625</t>
+  </si>
+  <si>
+    <t>0.75</t>
   </si>
   <si>
     <t>TP3</t>
   </si>
   <si>
-    <t>Lv_2_D1_West</t>
-  </si>
-  <si>
     <t>TP0</t>
   </si>
   <si>
-    <t>Lv_3_D1_East</t>
+    <t>Lv_3_Route_East</t>
   </si>
   <si>
     <t>Lv_3</t>
   </si>
   <si>
-    <t>Lv_3_Route_East</t>
-  </si>
-  <si>
-    <t>[Unit_Intern,2]</t>
+    <t>Unit_Intern</t>
+  </si>
+  <si>
+    <t>1.0375</t>
+  </si>
+  <si>
+    <t>0.9</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>Lv_3_D1_North</t>
+    <t>Lv_3_Route_North_BoneButcher</t>
   </si>
   <si>
     <t>Lv_3_Route_North</t>
   </si>
   <si>
-    <t>[Unit_BoneButcher_Lv2,1],[Unit_Intern,1]</t>
+    <t>18.9</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>Lv_3_D1_SouthEast</t>
+    <t>BoneButcher</t>
+  </si>
+  <si>
+    <t>Lv_3_Route_North_Intern</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>Intern</t>
   </si>
   <si>
     <t>Lv_3_Route_SouthEast</t>
@@ -282,7 +294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -295,6 +307,10 @@
     <col min="8" max="8" width="71.9030838012695" customWidth="1"/>
     <col min="9" max="9" width="43.4209403991699" customWidth="1"/>
     <col min="10" max="10" width="158.619125366211" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -339,40 +355,58 @@
       <c r="K2" s="0" t="s">
         <v>11</v>
       </c>
+      <c r="L2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="0" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -380,556 +414,615 @@
         <v>0</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B5" s="0">
         <v>1</v>
       </c>
+      <c r="C5" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D5" s="0" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="0">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>34</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>31</v>
+        <v>3</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B6" s="0">
         <v>2</v>
       </c>
+      <c r="C6" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D6" s="0" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="0">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>34</v>
       </c>
       <c r="G6" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="0">
+        <v>3</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="F7" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="0" t="s">
+      <c r="G7" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="0" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="0">
-        <v>3</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="I7" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="0">
-        <v>1</v>
-      </c>
-      <c r="G7" s="0" t="s">
+      <c r="J7" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>30</v>
-      </c>
       <c r="K7" s="0" t="s">
-        <v>38</v>
+        <v>3</v>
+      </c>
+      <c r="L7" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B8" s="0">
         <v>4</v>
       </c>
+      <c r="C8" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D8" s="0" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="0">
-        <v>2</v>
+        <v>48</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>49</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>35</v>
+        <v>3</v>
+      </c>
+      <c r="L8" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B9" s="0">
         <v>5</v>
       </c>
+      <c r="C9" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D9" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="0">
-        <v>2</v>
+        <v>48</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>49</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>31</v>
+        <v>3</v>
+      </c>
+      <c r="L9" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B10" s="0">
         <v>6</v>
       </c>
+      <c r="C10" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D10" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="0">
-        <v>2</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>38</v>
+      <c r="N10" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B11" s="0">
         <v>7</v>
       </c>
+      <c r="C11" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D11" s="0" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="0">
-        <v>3</v>
+        <v>57</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>34</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>35</v>
+        <v>3</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B12" s="0">
         <v>8</v>
       </c>
+      <c r="C12" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D12" s="0" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="0">
-        <v>3</v>
+        <v>57</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>34</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>31</v>
+        <v>3</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B13" s="0">
         <v>9</v>
       </c>
+      <c r="C13" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D13" s="0" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="0">
-        <v>3</v>
+        <v>57</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>34</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H13" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="0" t="s">
-        <v>3</v>
-      </c>
       <c r="J13" s="0" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>38</v>
+        <v>3</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="N13" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B14" s="0">
         <v>10</v>
       </c>
+      <c r="C14" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D14" s="0" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="0">
-        <v>4</v>
+        <v>64</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>34</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>35</v>
+        <v>3</v>
+      </c>
+      <c r="L14" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B15" s="0">
         <v>11</v>
       </c>
+      <c r="C15" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D15" s="0" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="0">
-        <v>4</v>
+        <v>64</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>34</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>31</v>
+        <v>3</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="N15" s="0" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B16" s="0">
         <v>12</v>
       </c>
+      <c r="C16" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D16" s="0" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="0">
-        <v>4</v>
+        <v>64</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>34</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>38</v>
+        <v>3</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="N16" s="0" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="B17" s="0">
         <v>13</v>
       </c>
+      <c r="C17" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="D17" s="0" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="0">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>34</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="0">
-        <v>14</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="0">
-        <v>1</v>
-      </c>
-      <c r="G18" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="I18" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="K18" s="0" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="0">
-        <v>15</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="0">
-        <v>1</v>
-      </c>
-      <c r="G19" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J19" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="0" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="0">
-        <v>16</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="0">
-        <v>1</v>
-      </c>
-      <c r="G20" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="K20" s="0" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="0">
-        <v>17</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="0">
-        <v>1</v>
-      </c>
-      <c r="G21" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="I21" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="0" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="0">
-        <v>18</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="0">
-        <v>1</v>
-      </c>
-      <c r="G22" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="K22" s="0" t="s">
-        <v>74</v>
+        <v>3</v>
+      </c>
+      <c r="L17" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="M17" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="N17" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Level/DefendAttackGroupTable.xlsx
+++ b/AAAGameData/DataTables/Level/DefendAttackGroupTable.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>#</t>
   </si>
@@ -131,7 +131,7 @@
     <t>31.5</t>
   </si>
   <si>
-    <t>0.2</t>
+    <t>0.2001953125</t>
   </si>
   <si>
     <t>15</t>
@@ -155,10 +155,10 @@
     <t>Unit_HiredBodyguard</t>
   </si>
   <si>
-    <t>5.188</t>
-  </si>
-  <si>
-    <t>0.8</t>
+    <t>5.188232421875</t>
+  </si>
+  <si>
+    <t>0.800048828125</t>
   </si>
   <si>
     <t>12,12,12</t>
@@ -191,36 +191,57 @@
     <t>0.5</t>
   </si>
   <si>
+    <t>0,0,0</t>
+  </si>
+  <si>
+    <t>2_4@Canmaker</t>
+  </si>
+  <si>
+    <t>2_4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>6,6,6</t>
+  </si>
+  <si>
+    <t>Canmaker</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>2_4@Brat</t>
   </si>
   <si>
-    <t>2_4</t>
+    <t>2,3</t>
   </si>
   <si>
     <t>Unit_Brat</t>
   </si>
   <si>
+    <t>6,6</t>
+  </si>
+  <si>
     <t>Brat</t>
   </si>
   <si>
-    <t>2_4@Canmaker</t>
-  </si>
-  <si>
-    <t>Canmaker</t>
+    <t>3_4</t>
   </si>
   <si>
     <t>2_4@HiredBodyguard</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>HiredBodyguard</t>
   </si>
   <si>
-    <t>3_4</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>2_1_0@North@BoneButcher</t>
   </si>
   <si>
@@ -230,7 +251,7 @@
     <t>2_1_0@North</t>
   </si>
   <si>
-    <t>18.9</t>
+    <t>18.900146484375</t>
   </si>
   <si>
     <t>14</t>
@@ -245,7 +266,7 @@
     <t>Unit_Intern</t>
   </si>
   <si>
-    <t>0.9</t>
+    <t>0.900146484375</t>
   </si>
   <si>
     <t>Intern</t>
@@ -254,7 +275,7 @@
     <t>4_3_0@SouthEast</t>
   </si>
   <si>
-    <t>1.038</t>
+    <t>1.0380859375</t>
   </si>
   <si>
     <t>20</t>
@@ -651,7 +672,7 @@
         <v>56</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>55</v>
@@ -660,13 +681,13 @@
         <v>57</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L11" s="0" t="s">
         <v>3</v>
@@ -677,31 +698,31 @@
         <v>8</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>56</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>58</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -709,31 +730,31 @@
         <v>9</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>56</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H13" s="0" t="s">
         <v>57</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>58</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -741,31 +762,31 @@
         <v>10</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>56</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>58</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -773,28 +794,28 @@
         <v>11</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>56</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>58</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L15" s="0" t="s">
         <v>3</v>
@@ -805,31 +826,31 @@
         <v>12</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>58</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -837,31 +858,31 @@
         <v>13</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>31</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H17" s="0" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>34</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
@@ -869,31 +890,31 @@
         <v>14</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>31</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I18" s="0" t="s">
         <v>58</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -901,28 +922,28 @@
         <v>15</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>31</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L19" s="0" t="s">
         <v>3</v>
@@ -933,28 +954,28 @@
         <v>16</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F20" s="0" t="s">
         <v>31</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L20" s="0" t="s">
         <v>3</v>
